--- a/basedatos_partidas/salida/descompuestos/CT-17-01-020.xlsx
+++ b/basedatos_partidas/salida/descompuestos/CT-17-01-020.xlsx
@@ -539,10 +539,10 @@
         <v>2.1</v>
       </c>
       <c r="G10" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="H10" t="n">
-        <v>33.6</v>
+        <v>39.9</v>
       </c>
     </row>
     <row r="11">
@@ -617,10 +617,10 @@
         <v>4</v>
       </c>
       <c r="G13" t="n">
-        <v>3.4</v>
+        <v>2.2</v>
       </c>
       <c r="H13" t="n">
-        <v>13.6</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="14">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>77.73999999999999</v>
+        <v>79.23999999999999</v>
       </c>
     </row>
     <row r="15">
@@ -828,10 +828,10 @@
         <v>1</v>
       </c>
       <c r="G25" t="n">
-        <v>93.22</v>
+        <v>94.72</v>
       </c>
       <c r="H25" t="n">
-        <v>0.93</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="26">
@@ -847,7 +847,7 @@
       </c>
       <c r="G26" s="4" t="n"/>
       <c r="H26" s="5" t="n">
-        <v>94.15000000000001</v>
+        <v>95.67</v>
       </c>
     </row>
   </sheetData>

--- a/basedatos_partidas/salida/descompuestos/CT-17-01-020.xlsx
+++ b/basedatos_partidas/salida/descompuestos/CT-17-01-020.xlsx
@@ -565,10 +565,10 @@
         <v>7</v>
       </c>
       <c r="G11" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="H11" t="n">
-        <v>29.4</v>
+        <v>31.5</v>
       </c>
     </row>
     <row r="12">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>79.23999999999999</v>
+        <v>81.34</v>
       </c>
     </row>
     <row r="15">
@@ -828,10 +828,10 @@
         <v>1</v>
       </c>
       <c r="G25" t="n">
-        <v>94.72</v>
+        <v>96.81999999999999</v>
       </c>
       <c r="H25" t="n">
-        <v>0.95</v>
+        <v>0.97</v>
       </c>
     </row>
     <row r="26">
@@ -847,7 +847,7 @@
       </c>
       <c r="G26" s="4" t="n"/>
       <c r="H26" s="5" t="n">
-        <v>95.67</v>
+        <v>97.79000000000001</v>
       </c>
     </row>
   </sheetData>

--- a/basedatos_partidas/salida/descompuestos/CT-17-01-020.xlsx
+++ b/basedatos_partidas/salida/descompuestos/CT-17-01-020.xlsx
@@ -438,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A3:H26"/>
+  <dimension ref="A1:H26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -451,6 +451,20 @@
     <col width="12" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Capítulo: 17 Equipamiento y mobiliario fijo</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Subcapítulo: Mobiliario de cocina</t>
+        </is>
+      </c>
+    </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
